--- a/utils.xlsx
+++ b/utils.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\doc-mailmerge\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\doc-mailmerge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB2FA65-795E-40DB-AC48-CDC7D88B7F45}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33F6E1B-8414-45E5-AF28-07DEEC065BA0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
@@ -18,8 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
   <si>
     <t>-</t>
   </si>
@@ -175,7 +174,34 @@
     <t>Системный администратор</t>
   </si>
   <si>
-    <t>всего9</t>
+    <t>1 года 10 месяцев</t>
+  </si>
+  <si>
+    <t>базовый</t>
+  </si>
+  <si>
+    <t>КОД 38.02.07-1-2026</t>
+  </si>
+  <si>
+    <t>КОД 44.02.01-1-2026</t>
+  </si>
+  <si>
+    <t>КОД 09.02.07-2-2026</t>
+  </si>
+  <si>
+    <t>КОД 44.02.02-1-2026</t>
+  </si>
+  <si>
+    <t>КОД 40.02.04-1-2026</t>
+  </si>
+  <si>
+    <t>КОД 15.01.05-1-2026</t>
+  </si>
+  <si>
+    <t>КОД 09.02.06-1-2026</t>
+  </si>
+  <si>
+    <t>профильный уровень</t>
   </si>
 </sst>
 </file>
@@ -200,7 +226,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -502,20 +528,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C689DA-FB91-4EAC-AF04-73C653425B7D}">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="5" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.5546875" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -540,11 +566,8 @@
       <c r="H1" t="s">
         <v>40</v>
       </c>
-      <c r="I1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -557,11 +580,11 @@
       <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="3" t="s">
         <v>34</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>39</v>
@@ -569,9 +592,17 @@
       <c r="H2" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -596,9 +627,17 @@
       <c r="H3" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -611,10 +650,10 @@
       <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -623,9 +662,17 @@
       <c r="H4" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -650,9 +697,17 @@
       <c r="H5" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -677,9 +732,17 @@
       <c r="H6" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -704,9 +767,17 @@
       <c r="H7" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -719,10 +790,10 @@
       <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -731,9 +802,8 @@
       <c r="H8" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -746,11 +816,11 @@
       <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E9" s="3" t="s">
         <v>34</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>39</v>
@@ -758,9 +828,8 @@
       <c r="H9" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -785,9 +854,17 @@
       <c r="H10" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -812,9 +889,17 @@
       <c r="H11" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -839,7 +924,15 @@
       <c r="H12" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="3"/>
+      <c r="I12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{D75D259A-D141-43DD-ABB3-FA5CE787CCCA}">

--- a/utils.xlsx
+++ b/utils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\doc-mailmerge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33F6E1B-8414-45E5-AF28-07DEEC065BA0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C022C-33F2-4605-A20A-516C0C84B70A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="75">
   <si>
     <t>-</t>
   </si>
@@ -202,19 +203,119 @@
   </si>
   <si>
     <t>профильный уровень</t>
+  </si>
+  <si>
+    <t>ПНД-4</t>
+  </si>
+  <si>
+    <t>1. Правоохранительная деятельность
+2. Обеспечение реализации прав граждан в сфере пенсионного обеспечения и социальной защиты</t>
+  </si>
+  <si>
+    <t>1. Автоматизированное рабочее место (АРМ) в комплекте: системный блок – ОЗУ , HDD, монитор, клавиатура, мышь, звуковые колонки, офисный пакет приложений, операционная система, специализированное ПО. 
+2. Многофункциональный интерактивный комплекс. 
+3. Организационная техника</t>
+  </si>
+  <si>
+    <t>Государственное бюджетное профессиональное образовательное учреждение «Кабардино-Балкарский гуманитарно-технический колледж»</t>
+  </si>
+  <si>
+    <t>1. Правоприменительная деятельность
+2. Правоохранительная деятельность
+3. Организационно-техническое обеспечение работы судов
+4. Обеспечение реализации прав граждан в сфере пенсионного обеспечения и социальной защиты</t>
+  </si>
+  <si>
+    <t>1. Правоприменительная деятельность
+2. Правоохранительная деятельность
+3.Организационно-техническое обеспечение работы судов
+4. Обеспечение реализации прав граждан в сфере пенсионного обеспечения и социальной защиты</t>
+  </si>
+  <si>
+    <t>Виды деятельности</t>
+  </si>
+  <si>
+    <t>Использованные средства обучения</t>
+  </si>
+  <si>
+    <t>Место прохождения</t>
+  </si>
+  <si>
+    <t>ЮЗ-50</t>
+  </si>
+  <si>
+    <t>40.02.02 Правоохранительная деятельность</t>
+  </si>
+  <si>
+    <t>2 года 6 месяцев</t>
+  </si>
+  <si>
+    <t>3 года 6 месяцев</t>
+  </si>
+  <si>
+    <t>Специалист по документационному обеспечению управления и архивному делу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Квалификация </t>
+  </si>
+  <si>
+    <t>Программа</t>
+  </si>
+  <si>
+    <t>21299 Делопроизводитель</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -231,7 +332,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -239,15 +340,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -528,56 +674,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C689DA-FB91-4EAC-AF04-73C653425B7D}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="69.109375" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.5546875" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>46188</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -586,68 +758,68 @@
       <c r="F2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>46196</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>46197</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -656,164 +828,194 @@
       <c r="F4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>46190</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>46195</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46195</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C8" s="2">
         <v>46192</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K7">
+      <c r="K8" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="L8" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C9" s="2">
         <v>46183</v>
       </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="1">
-        <v>46184</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -822,121 +1024,191 @@
       <c r="F9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46184</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K10">
+      <c r="K11" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C12" s="2">
         <v>46189</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K11">
+      <c r="K12" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C13" s="2">
         <v>46191</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K12">
+      <c r="K13" s="1">
         <v>75</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{D75D259A-D141-43DD-ABB3-FA5CE787CCCA}">
-    <sortState ref="A2:D12">
+    <sortState ref="A2:D13">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>

--- a/utils.xlsx
+++ b/utils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\doc-mailmerge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C022C-33F2-4605-A20A-516C0C84B70A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24600951-CCD7-48E1-8355-19BBEE593204}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="75">
-  <si>
-    <t>-</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="77">
   <si>
     <t>40.02.04 Юриспруденция</t>
   </si>
@@ -176,9 +172,6 @@
   </si>
   <si>
     <t>1 года 10 месяцев</t>
-  </si>
-  <si>
-    <t>базовый</t>
   </si>
   <si>
     <t>КОД 38.02.07-1-2026</t>
@@ -259,10 +252,22 @@
     <t xml:space="preserve">Квалификация </t>
   </si>
   <si>
-    <t>Программа</t>
-  </si>
-  <si>
     <t>21299 Делопроизводитель</t>
+  </si>
+  <si>
+    <t>ПСЗ-9-6</t>
+  </si>
+  <si>
+    <t>ОЭВМ-5</t>
+  </si>
+  <si>
+    <t>Оператор электронно-вычислительных и вычислительных машин (2-й разряд)</t>
+  </si>
+  <si>
+    <t>16199 Оператор электронно-вычислительных и вычислительных машин</t>
+  </si>
+  <si>
+    <t>базовый уровень</t>
   </si>
 </sst>
 </file>
@@ -318,7 +323,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,6 +333,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -393,6 +404,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -674,276 +694,275 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C689DA-FB91-4EAC-AF04-73C653425B7D}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.77734375" style="14" customWidth="1"/>
     <col min="3" max="3" width="10.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" style="1" customWidth="1"/>
     <col min="9" max="9" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="11" max="16" width="8.88671875" style="1"/>
+    <col min="17" max="17" width="14.109375" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="E1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>66</v>
-      </c>
       <c r="O1" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>7</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="C2" s="2">
         <v>46188</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K2" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="C3" s="2">
         <v>46196</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K3" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="C4" s="2">
         <v>46197</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K4" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>46190</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K5" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="C6" s="2">
         <v>46195</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K6" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>56</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>46195</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K7" s="1">
         <v>75</v>
@@ -951,177 +970,177 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>2</v>
       </c>
       <c r="C8" s="2">
         <v>46192</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K8" s="1">
         <v>75</v>
       </c>
       <c r="L8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="N8" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>62</v>
-      </c>
       <c r="P8" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>4</v>
       </c>
       <c r="C9" s="2">
         <v>46183</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="C10" s="2">
         <v>46184</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46191</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="K11" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>8</v>
       </c>
       <c r="C12" s="2">
         <v>46189</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K12" s="1">
         <v>75</v>
@@ -1129,81 +1148,160 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>0</v>
       </c>
       <c r="C13" s="2">
         <v>46191</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K13" s="1">
         <v>75</v>
       </c>
       <c r="L13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="M13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="N13" s="9" t="s">
+      <c r="O13" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="O13" s="9" t="s">
-        <v>63</v>
-      </c>
       <c r="P13" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="12">
+        <v>46184</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="12">
+        <v>46184</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="1">
+        <v>75</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46198</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>45</v>
+      <c r="R16" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/utils.xlsx
+++ b/utils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\doc-mailmerge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24600951-CCD7-48E1-8355-19BBEE593204}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF701AC-2323-4CD2-B20B-D646DB1DAE08}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="75">
   <si>
     <t>40.02.04 Юриспруденция</t>
   </si>
@@ -42,9 +42,6 @@
     <t>ПСД-35</t>
   </si>
   <si>
-    <t>40.02.01 Право и организация социального обеспечения»</t>
-  </si>
-  <si>
     <t>ПСЗ-9</t>
   </si>
   <si>
@@ -201,30 +198,9 @@
     <t>ПНД-4</t>
   </si>
   <si>
-    <t>1. Правоохранительная деятельность
-2. Обеспечение реализации прав граждан в сфере пенсионного обеспечения и социальной защиты</t>
-  </si>
-  <si>
-    <t>1. Автоматизированное рабочее место (АРМ) в комплекте: системный блок – ОЗУ , HDD, монитор, клавиатура, мышь, звуковые колонки, офисный пакет приложений, операционная система, специализированное ПО. 
-2. Многофункциональный интерактивный комплекс. 
-3. Организационная техника</t>
-  </si>
-  <si>
     <t>Государственное бюджетное профессиональное образовательное учреждение «Кабардино-Балкарский гуманитарно-технический колледж»</t>
   </si>
   <si>
-    <t>1. Правоприменительная деятельность
-2. Правоохранительная деятельность
-3. Организационно-техническое обеспечение работы судов
-4. Обеспечение реализации прав граждан в сфере пенсионного обеспечения и социальной защиты</t>
-  </si>
-  <si>
-    <t>1. Правоприменительная деятельность
-2. Правоохранительная деятельность
-3.Организационно-техническое обеспечение работы судов
-4. Обеспечение реализации прав граждан в сфере пенсионного обеспечения и социальной защиты</t>
-  </si>
-  <si>
     <t>Виды деятельности</t>
   </si>
   <si>
@@ -268,13 +244,22 @@
   </si>
   <si>
     <t>базовый уровень</t>
+  </si>
+  <si>
+    <t>1. Правоохранительная деятельность*2. Обеспечение реализации прав граждан в сфере пенсионного обеспечения и социальной защиты</t>
+  </si>
+  <si>
+    <t>1. Автоматизированное рабочее место (АРМ) в комплекте: системный блок – ОЗУ , HDD, монитор, клавиатура, мышь, звуковые колонки, офисный пакет приложений, операционная система, специализированное ПО*2. Многофункциональный интерактивный комплекс*3. Организационная техника*</t>
+  </si>
+  <si>
+    <t>1. Правоприменительная деятельность*2. Правоохранительная деятельность*3. Организационно-техническое обеспечение работы судов*4. Обеспечение реализации прав граждан в сфере пенсионного обеспечения и социальной защиты*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,14 +282,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -370,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -390,19 +367,16 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -698,7 +672,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.77734375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="35.77734375" style="13" customWidth="1"/>
     <col min="3" max="3" width="10.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -713,81 +687,81 @@
   <sheetData>
     <row r="1" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="E1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="C2" s="2">
         <v>46188</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K2" s="1">
         <v>75</v>
@@ -795,34 +769,34 @@
     </row>
     <row r="3" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="14" t="s">
         <v>12</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="2">
         <v>46196</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K3" s="1">
         <v>75</v>
@@ -830,34 +804,34 @@
     </row>
     <row r="4" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>11</v>
       </c>
       <c r="C4" s="2">
         <v>46197</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K4" s="1">
         <v>75</v>
@@ -865,34 +839,34 @@
     </row>
     <row r="5" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="14" t="s">
         <v>10</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="C5" s="2">
         <v>46190</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K5" s="1">
         <v>75</v>
@@ -900,34 +874,34 @@
     </row>
     <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="14" t="s">
         <v>15</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="C6" s="2">
         <v>46195</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K6" s="1">
         <v>75</v>
@@ -935,34 +909,34 @@
     </row>
     <row r="7" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>15</v>
+        <v>55</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>14</v>
       </c>
       <c r="C7" s="2">
         <v>46195</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K7" s="1">
         <v>75</v>
@@ -972,140 +946,140 @@
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="2">
         <v>46192</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K8" s="1">
         <v>75</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>58</v>
+      <c r="L8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="14" t="s">
         <v>4</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="C9" s="2">
         <v>46183</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>29</v>
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="C10" s="2">
         <v>46184</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="14" t="s">
         <v>17</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="C11" s="2">
         <v>46191</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K11" s="1">
         <v>50</v>
@@ -1113,34 +1087,34 @@
     </row>
     <row r="12" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="14" t="s">
         <v>8</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>7</v>
       </c>
       <c r="C12" s="2">
         <v>46189</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="K12" s="1">
         <v>75</v>
@@ -1150,158 +1124,158 @@
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="2">
         <v>46191</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K13" s="1">
         <v>75</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="12">
+        <v>60</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="11">
         <v>46184</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>67</v>
+        <v>20</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>46184</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K15" s="1">
         <v>75</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C16" s="2">
         <v>46198</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
